--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N58_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N58_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>71.48403519960308</v>
+        <v>11.6161557199355</v>
       </c>
       <c r="D2" t="n">
-        <v>70.48186211352029</v>
+        <v>11.45330259344705</v>
       </c>
       <c r="E2" t="n">
-        <v>31.9073743701184</v>
+        <v>5.184948335144241</v>
       </c>
       <c r="F2" t="n">
-        <v>31.30497971705336</v>
+        <v>5.087059204021172</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3.294802258331788</v>
+        <v>0.5354053669789155</v>
       </c>
       <c r="D3" t="n">
-        <v>3.311566524351744</v>
+        <v>0.5381295602071584</v>
       </c>
       <c r="E3" t="n">
-        <v>31.9073743701184</v>
+        <v>5.184948335144241</v>
       </c>
       <c r="F3" t="n">
-        <v>31.30497971705336</v>
+        <v>5.087059204021172</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>4.313236822075885</v>
+        <v>0.7009009835873312</v>
       </c>
       <c r="D4" t="n">
-        <v>4.863583957841981</v>
+        <v>0.7903323931493219</v>
       </c>
       <c r="E4" t="n">
-        <v>31.9073743701184</v>
+        <v>5.184948335144241</v>
       </c>
       <c r="F4" t="n">
-        <v>31.30497971705336</v>
+        <v>5.087059204021172</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
